--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574864896</v>
+        <v>46157.93118972339</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93118972339</v>
+        <v>46157.9318419675</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9318419675</v>
+        <v>46157.93406195426</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93406195426</v>
+        <v>46157.93724220923</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93724220923</v>
+        <v>46158.28221981521</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221981521</v>
+        <v>46158.29703105235</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29703105235</v>
+        <v>46158.29821813867</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29821813867</v>
+        <v>46158.33392945705</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392945705</v>
+        <v>46158.36862729725</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лукаш- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862729725</v>
+        <v>46158.3729370251</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
